--- a/data.mn/public/datasets/mrpam-commodity-prices.xlsx
+++ b/data.mn/public/datasets/mrpam-commodity-prices.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,8 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E977"/>
+  <dimension ref="A1:E992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -20935,6 +20942,321 @@
         <v>3539.93</v>
       </c>
       <c r="E977" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B978" t="n">
+        <v>7</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>13524.52</v>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B979" t="n">
+        <v>7</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Fluorspar concentrate FF-97</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>520</v>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B980" t="n">
+        <v>7</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Fluorspar ore FK-85</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>425</v>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B981" t="n">
+        <v>7</v>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>4077.8</v>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>USD/troy oz</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B982" t="n">
+        <v>7</v>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Iron concentrate, 60%</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B983" t="n">
+        <v>7</v>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Iron ore, 56%</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B984" t="n">
+        <v>7</v>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>1843.55</v>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B985" t="n">
+        <v>7</v>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Manganese, 36%</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>193.9</v>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B986" t="n">
+        <v>7</v>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Molybdenum</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>70211.39999999999</v>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B987" t="n">
+        <v>7</v>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>USD/troy oz</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B988" t="n">
+        <v>7</v>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Tin</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>53088.8</v>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B989" t="n">
+        <v>7</v>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Tungsten, 65%</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>62943.87</v>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B990" t="n">
+        <v>7</v>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Tungsten, 99%</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>205652.17</v>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B991" t="n">
+        <v>7</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Uranium</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>190.43</v>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B992" t="n">
+        <v>7</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>3595.53</v>
+      </c>
+      <c r="E992" t="inlineStr">
         <is>
           <t>USD/tonne</t>
         </is>
@@ -20951,8 +21273,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E977"/>
+  <dimension ref="A1:E992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -41472,6 +41801,321 @@
         <v>3539.93</v>
       </c>
       <c r="E977" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B978" t="n">
+        <v>7</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Алт</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>4077.8</v>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>ам.долл/унци</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B979" t="n">
+        <v>7</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Гянтболд, 65%</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>62943.87</v>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B980" t="n">
+        <v>7</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Гянтболд, 99%</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>205652.17</v>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B981" t="n">
+        <v>7</v>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Жонш, баяжмал ФФ-97</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>520</v>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B982" t="n">
+        <v>7</v>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Жонш, хүдэр ФК-85</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>425</v>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B983" t="n">
+        <v>7</v>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Зэс</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>13524.52</v>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B984" t="n">
+        <v>7</v>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Манган, 36%</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>193.9</v>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B985" t="n">
+        <v>7</v>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Молибдени</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>70211.39999999999</v>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B986" t="n">
+        <v>7</v>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Мөнгө</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>ам.долл/унци</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B987" t="n">
+        <v>7</v>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Төмөр, 56% хүдэр</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B988" t="n">
+        <v>7</v>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Төмөр, 60% баяжмал</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B989" t="n">
+        <v>7</v>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Уран</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>190.43</v>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>ам.долл/кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B990" t="n">
+        <v>7</v>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Хар тугалга</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>1843.55</v>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B991" t="n">
+        <v>7</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Цагаан тугалга</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>53088.8</v>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>ам.долл/тн</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B992" t="n">
+        <v>7</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Цайр</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>3595.53</v>
+      </c>
+      <c r="E992" t="inlineStr">
         <is>
           <t>ам.долл/тн</t>
         </is>
